--- a/data/trans_camb/P6905-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 3,09</t>
+          <t>-23,94; 3,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 7,76</t>
+          <t>-20,46; 8,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 7,02</t>
+          <t>-30,67; 6,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 25,41</t>
+          <t>-12,17; 27,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 49,74</t>
+          <t>-3,74; 47,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 54,75</t>
+          <t>-2,53; 61,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 7,56</t>
+          <t>-13,85; 9,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,73; 14,35</t>
+          <t>-11,91; 13,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 22,56</t>
+          <t>-15,11; 24,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-71,68; 14,07</t>
+          <t>-73,7; 15,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 36,22</t>
+          <t>-62,66; 37,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-97,99; 32,4</t>
+          <t>-97,85; 53,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 213,03</t>
+          <t>-43,37; 221,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 391,0</t>
+          <t>-18,62; 394,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 509,28</t>
+          <t>-19,28; 710,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-49,89; 34,93</t>
+          <t>-46,19; 44,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-39,8; 70,77</t>
+          <t>-40,79; 63,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 100,2</t>
+          <t>-52,88; 114,42</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 7,79</t>
+          <t>-9,58; 7,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,36</t>
+          <t>-11,03; 4,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -1,11</t>
+          <t>-16,46; 0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 7,82</t>
+          <t>-16,99; 8,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 8,8</t>
+          <t>-16,11; 9,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,25; -10,49</t>
+          <t>-35,17; -9,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 5,95</t>
+          <t>-8,32; 5,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 4,62</t>
+          <t>-9,05; 4,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,43; -4,35</t>
+          <t>-17,97; -4,2</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 28,52</t>
+          <t>-28,25; 27,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,18; 16,65</t>
+          <t>-33,82; 19,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,7; -4,46</t>
+          <t>-49,6; 1,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,94; 19,6</t>
+          <t>-32,69; 20,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,95; 20,44</t>
+          <t>-31,02; 24,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,96; -25,44</t>
+          <t>-66,58; -23,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,35; 18,69</t>
+          <t>-21,94; 18,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,9; 15,15</t>
+          <t>-24,42; 14,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,94; -14,29</t>
+          <t>-48,83; -14,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 5,4</t>
+          <t>-27,91; 7,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 15,6</t>
+          <t>-19,11; 15,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,57; 18,06</t>
+          <t>-18,83; 19,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 28,21</t>
+          <t>-13,1; 25,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 14,54</t>
+          <t>-19,15; 14,16</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 18,85</t>
+          <t>-11,49; 18,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,92; 12,23</t>
+          <t>-14,73; 12,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 10,56</t>
+          <t>-14,47; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 13,53</t>
+          <t>-9,17; 13,84</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,28; 21,46</t>
+          <t>-64,92; 29,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,81; 54,12</t>
+          <t>-44,09; 56,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 69,91</t>
+          <t>-44,63; 68,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-25,23; 94,16</t>
+          <t>-29,21; 84,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-41,74; 49,1</t>
+          <t>-42,74; 46,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 62,92</t>
+          <t>-24,69; 65,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 38,97</t>
+          <t>-34,3; 39,59</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-31,73; 34,32</t>
+          <t>-33,86; 29,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,84; 44,65</t>
+          <t>-21,19; 45,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 2,95</t>
+          <t>-10,27; 2,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,52; 3,82</t>
+          <t>-9,83; 3,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,33; -0,27</t>
+          <t>-14,08; -0,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 10,02</t>
+          <t>-9,5; 9,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 9,98</t>
+          <t>-9,64; 9,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,92; -0,77</t>
+          <t>-19,77; 0,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 4,23</t>
+          <t>-6,77; 4,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 4,3</t>
+          <t>-6,63; 4,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-11,92; -0,57</t>
+          <t>-12,31; -0,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 10,54</t>
+          <t>-31,75; 9,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-29,13; 14,5</t>
+          <t>-30,04; 14,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,39; -0,55</t>
+          <t>-43,54; -2,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 27,22</t>
+          <t>-21,26; 25,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 27,17</t>
+          <t>-20,72; 26,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-44,96; -2,23</t>
+          <t>-43,77; -0,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-18,25; 13,91</t>
+          <t>-19,12; 13,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 14,01</t>
+          <t>-17,78; 14,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,25; -1,82</t>
+          <t>-34,68; -1,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6905-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P6905-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-18,05</t>
+          <t>-14,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,73</t>
+          <t>7,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>-6,42</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 3,14</t>
+          <t>-23,85; 3,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-20,46; 8,36</t>
+          <t>-19,51; 8,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,67; 6,82</t>
+          <t>-28,35; 3,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 27,31</t>
+          <t>-12,67; 24,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 47,31</t>
+          <t>-6,32; 48,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 61,26</t>
+          <t>-12,6; 27,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 9,18</t>
+          <t>-15,55; 7,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 13,95</t>
+          <t>-11,63; 12,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 24,85</t>
+          <t>-16,95; 8,49</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-65,5%</t>
+          <t>-52,55%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>102,93%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,5%</t>
+          <t>-24,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-73,7; 15,59</t>
+          <t>-72,3; 16,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,66; 37,64</t>
+          <t>-60,81; 42,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-97,85; 53,23</t>
+          <t>-89,91; 26,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 221,03</t>
+          <t>-41,37; 211,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 394,72</t>
+          <t>-24,91; 369,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 710,0</t>
+          <t>-42,0; 256,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,19; 44,78</t>
+          <t>-50,99; 33,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,79; 63,14</t>
+          <t>-39,42; 61,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 114,42</t>
+          <t>-56,3; 43,18</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-8,73</t>
+          <t>-7,25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-20,71</t>
+          <t>-17,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-10,87</t>
+          <t>-8,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 7,38</t>
+          <t>-9,51; 7,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 4,99</t>
+          <t>-12,11; 4,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 0,19</t>
+          <t>-14,96; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,99; 8,46</t>
+          <t>-18,68; 7,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 9,84</t>
+          <t>-17,17; 8,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -9,45</t>
+          <t>-27,86; -6,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 5,71</t>
+          <t>-8,48; 5,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 4,68</t>
+          <t>-9,39; 4,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -4,2</t>
+          <t>-15,26; -2,36</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-29,59%</t>
+          <t>-24,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-43,11%</t>
+          <t>-35,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,14%</t>
+          <t>-25,28%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 27,7</t>
+          <t>-27,74; 27,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 19,04</t>
+          <t>-37,81; 17,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,6; 1,24</t>
+          <t>-45,37; 5,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 20,97</t>
+          <t>-34,45; 17,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,02; 24,18</t>
+          <t>-30,79; 20,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -23,48</t>
+          <t>-50,45; -15,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 18,74</t>
+          <t>-22,32; 18,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 14,89</t>
+          <t>-25,13; 14,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-48,83; -14,33</t>
+          <t>-39,8; -7,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>5,75</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,04</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>3,95</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,91; 7,29</t>
+          <t>-27,54; 7,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 15,73</t>
+          <t>-17,53; 15,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 19,18</t>
+          <t>-10,87; 24,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 25,54</t>
+          <t>-11,46; 26,19</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 14,16</t>
+          <t>-19,74; 13,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 18,59</t>
+          <t>-14,23; 16,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,73; 12,09</t>
+          <t>-13,7; 12,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,47; 9,91</t>
+          <t>-13,1; 10,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-9,17; 13,84</t>
+          <t>-6,59; 15,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,92; 29,45</t>
+          <t>-65,19; 29,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 56,18</t>
+          <t>-40,62; 55,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,63; 68,25</t>
+          <t>-28,33; 84,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,21; 84,41</t>
+          <t>-24,42; 87,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,74; 46,09</t>
+          <t>-41,38; 47,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,69; 65,6</t>
+          <t>-27,78; 56,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-34,3; 39,59</t>
+          <t>-34,02; 39,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,86; 29,51</t>
+          <t>-31,49; 33,62</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 45,33</t>
+          <t>-15,91; 47,68</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,12</t>
+          <t>-4,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-8,65</t>
+          <t>-7,33</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-5,79</t>
+          <t>-4,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 2,72</t>
+          <t>-10,87; 2,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 3,57</t>
+          <t>-9,95; 3,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,08; -0,77</t>
+          <t>-11,4; 2,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 9,37</t>
+          <t>-10,16; 9,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 9,53</t>
+          <t>-7,8; 11,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-19,77; 0,22</t>
+          <t>-15,52; 1,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 4,34</t>
+          <t>-7,66; 3,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 4,53</t>
+          <t>-6,88; 4,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,31; -0,45</t>
+          <t>-9,1; 0,7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-23,7%</t>
+          <t>-15,74%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-21,11%</t>
+          <t>-17,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-17,27%</t>
+          <t>-12,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-31,75; 9,74</t>
+          <t>-32,49; 7,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,04; 14,12</t>
+          <t>-30,66; 12,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,54; -2,46</t>
+          <t>-35,88; 8,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 25,63</t>
+          <t>-22,32; 26,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 26,01</t>
+          <t>-17,72; 32,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,77; -0,13</t>
+          <t>-33,26; 3,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,12; 13,76</t>
+          <t>-20,91; 12,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 14,53</t>
+          <t>-19,38; 13,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,68; -1,74</t>
+          <t>-25,07; 2,63</t>
         </is>
       </c>
     </row>
